--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1876,7 +1876,7 @@
         <v>122743360</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>122743379</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R12" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R13" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R12" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R13" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R12" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R13" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R12" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R13" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R12" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R13" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1876,7 +1876,7 @@
         <v>122743360</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>122743379</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 23574-2024 artfynd.xlsx
+++ b/artfynd/A 23574-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743360</v>
+        <v>122743379</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>90975</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679942</v>
+        <v>679800</v>
       </c>
       <c r="R12" t="n">
-        <v>7069410</v>
+        <v>7069436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743379</v>
+        <v>122743360</v>
       </c>
       <c r="B13" t="n">
-        <v>90973</v>
+        <v>90957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679800</v>
+        <v>679942</v>
       </c>
       <c r="R13" t="n">
-        <v>7069436</v>
+        <v>7069410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
